--- a/crates/forskscope-core/src/tests/fixtures/xlsx/unchanged_sheet/old.xlsx
+++ b/crates/forskscope-core/src/tests/fixtures/xlsx/unchanged_sheet/old.xlsx
@@ -17,10 +17,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
-    <t>const</t>
+    <t>same</t>
   </si>
   <si>
-    <t>a</t>
+    <t>before</t>
   </si>
 </sst>
 </file>
